--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D175BC73-0FA1-4D6A-B497-53F936E7E1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4EA2BC-131A-49EE-B0FF-FCFB86004990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关卡|Level" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -102,6 +102,14 @@
   </si>
   <si>
     <t>Level_6</t>
+  </si>
+  <si>
+    <t>rewardId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡奖励id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -182,7 +190,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -205,15 +213,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -224,13 +223,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -517,7 +515,7 @@
     <col min="1" max="1" width="9.25" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
     <col min="3" max="3" width="12.375" customWidth="1"/>
-    <col min="4" max="4" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -528,10 +526,12 @@
         <v>1</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="F1"/>
       <c r="G1"/>
       <c r="H1"/>
@@ -562,10 +562,12 @@
         <v>3</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
@@ -595,7 +597,7 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
+      <c r="E3" s="4"/>
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3"/>
@@ -622,16 +624,18 @@
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4"/>
@@ -658,51 +662,69 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
+      <c r="A6" s="6"/>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6" t="s">
         <v>12</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>13</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>15</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>6</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>16</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4EA2BC-131A-49EE-B0FF-FCFB86004990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A69D03B-694B-484C-9E39-33E3A272AFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="3090" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关卡|Level" sheetId="1" r:id="rId1"/>
@@ -667,7 +667,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="6">
-        <v>1</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="6">
-        <v>1</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
@@ -691,7 +691,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="6">
-        <v>1</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
@@ -702,7 +702,7 @@
         <v>14</v>
       </c>
       <c r="E8" s="6">
-        <v>1</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
@@ -713,7 +713,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="6">
-        <v>1</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
@@ -724,7 +724,7 @@
         <v>16</v>
       </c>
       <c r="E10" s="6">
-        <v>1</v>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A69D03B-694B-484C-9E39-33E3A272AFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFE0F47-DAE6-45E6-B8F3-4A2475655B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="3090" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关卡|Level" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -110,6 +110,78 @@
   <si>
     <t>关卡奖励id</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level_7</t>
+  </si>
+  <si>
+    <t>Level_8</t>
+  </si>
+  <si>
+    <t>Level_9</t>
+  </si>
+  <si>
+    <t>Level_10</t>
+  </si>
+  <si>
+    <t>Level_11</t>
+  </si>
+  <si>
+    <t>Level_12</t>
+  </si>
+  <si>
+    <t>Level_13</t>
+  </si>
+  <si>
+    <t>Level_14</t>
+  </si>
+  <si>
+    <t>Level_15</t>
+  </si>
+  <si>
+    <t>Level_16</t>
+  </si>
+  <si>
+    <t>Level_17</t>
+  </si>
+  <si>
+    <t>Level_18</t>
+  </si>
+  <si>
+    <t>Level_19</t>
+  </si>
+  <si>
+    <t>Level_20</t>
+  </si>
+  <si>
+    <t>Level_21</t>
+  </si>
+  <si>
+    <t>Level_22</t>
+  </si>
+  <si>
+    <t>Level_23</t>
+  </si>
+  <si>
+    <t>Level_24</t>
+  </si>
+  <si>
+    <t>Level_25</t>
+  </si>
+  <si>
+    <t>Level_26</t>
+  </si>
+  <si>
+    <t>Level_27</t>
+  </si>
+  <si>
+    <t>Level_28</t>
+  </si>
+  <si>
+    <t>Level_29</t>
+  </si>
+  <si>
+    <t>Level_30</t>
   </si>
 </sst>
 </file>
@@ -509,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -667,7 +739,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="6">
-        <v>10000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
@@ -725,6 +797,270 @@
       </c>
       <c r="E10" s="6">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>22</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>23</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>24</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>25</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>26</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>27</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>28</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B33">
+        <v>29</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B34">
+        <v>30</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="6">
+        <v>10001</v>
       </c>
     </row>
   </sheetData>

--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFE0F47-DAE6-45E6-B8F3-4A2475655B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F8CADA-937D-4C0E-9ED2-FFAF7F8566E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关卡|Level" sheetId="1" r:id="rId1"/>

--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F8CADA-937D-4C0E-9ED2-FFAF7F8566E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604EDBC3-5E58-4FAC-A80C-502EBD6B32E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关卡|Level" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -182,6 +182,36 @@
   </si>
   <si>
     <t>Level_30</t>
+  </si>
+  <si>
+    <t>Level_31</t>
+  </si>
+  <si>
+    <t>Level_32</t>
+  </si>
+  <si>
+    <t>Level_33</t>
+  </si>
+  <si>
+    <t>Level_34</t>
+  </si>
+  <si>
+    <t>Level_35</t>
+  </si>
+  <si>
+    <t>Level_36</t>
+  </si>
+  <si>
+    <t>Level_37</t>
+  </si>
+  <si>
+    <t>Level_38</t>
+  </si>
+  <si>
+    <t>Level_39</t>
+  </si>
+  <si>
+    <t>Level_40</t>
   </si>
 </sst>
 </file>
@@ -581,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1063,6 +1093,116 @@
         <v>10001</v>
       </c>
     </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B35">
+        <v>31</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B36">
+        <v>32</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B37">
+        <v>33</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B38">
+        <v>34</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B39">
+        <v>35</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>36</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B41">
+        <v>37</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <v>38</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>39</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B44">
+        <v>40</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="6">
+        <v>10001</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604EDBC3-5E58-4FAC-A80C-502EBD6B32E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C1A755-1EBD-46A6-8102-02866E04E641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -35,6 +35,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -45,6 +46,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -212,6 +214,51 @@
   </si>
   <si>
     <t>Level_40</t>
+  </si>
+  <si>
+    <t>Level_41</t>
+  </si>
+  <si>
+    <t>Level_42</t>
+  </si>
+  <si>
+    <t>Level_43</t>
+  </si>
+  <si>
+    <t>Level_44</t>
+  </si>
+  <si>
+    <t>Level_45</t>
+  </si>
+  <si>
+    <t>Level_46</t>
+  </si>
+  <si>
+    <t>Level_47</t>
+  </si>
+  <si>
+    <t>Level_48</t>
+  </si>
+  <si>
+    <t>Level_49</t>
+  </si>
+  <si>
+    <t>Level_50</t>
+  </si>
+  <si>
+    <t>Level_51</t>
+  </si>
+  <si>
+    <t>Level_52</t>
+  </si>
+  <si>
+    <t>Level_53</t>
+  </si>
+  <si>
+    <t>Level_54</t>
+  </si>
+  <si>
+    <t>Level_55</t>
   </si>
 </sst>
 </file>
@@ -230,6 +277,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -237,6 +285,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -611,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z44"/>
+  <dimension ref="A1:Z59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -815,7 +864,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="6">
-        <v>10000</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
@@ -925,7 +974,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="6">
-        <v>10000</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
@@ -1035,7 +1084,7 @@
         <v>37</v>
       </c>
       <c r="E29" s="6">
-        <v>10000</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
@@ -1145,7 +1194,7 @@
         <v>47</v>
       </c>
       <c r="E39" s="6">
-        <v>10000</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.2">
@@ -1201,6 +1250,171 @@
       </c>
       <c r="E44" s="6">
         <v>10001</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B45">
+        <v>41</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B46">
+        <v>42</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B47">
+        <v>43</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E47" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B48">
+        <v>44</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B49">
+        <v>45</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B50">
+        <v>46</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B51">
+        <v>47</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B52">
+        <v>48</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B53">
+        <v>49</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B54">
+        <v>50</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B55">
+        <v>51</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B56">
+        <v>52</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B57">
+        <v>53</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E57" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B58">
+        <v>54</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B59">
+        <v>55</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E59" s="6">
+        <v>10002</v>
       </c>
     </row>
   </sheetData>
